--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T19:39:21+00:00</t>
+    <t>2024-11-14T19:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T19:54:42+00:00</t>
+    <t>2024-11-29T17:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T17:24:43+00:00</t>
+    <t>2024-11-29T17:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/ext-radiation-level-score</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/ext-radiation-level-score</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T17:24:50+00:00</t>
+    <t>2024-12-05T15:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
   </si>
   <si>
     <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T15:44:48+00:00</t>
+    <t>2024-12-05T15:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T15:45:34+00:00</t>
+    <t>2024-12-05T15:45:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/ext-radiation-level-score</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/ext-radiation-level-score</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T15:45:53+00:00</t>
+    <t>2024-12-11T15:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>HL7 Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
   </si>
   <si>
     <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T15:33:45+00:00</t>
+    <t>2024-12-11T16:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T16:17:48+00:00</t>
+    <t>2024-12-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T15:55:45+00:00</t>
+    <t>2024-12-23T16:34:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="105">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>ID</t>
   </si>
   <si>
-    <t>cpg-rating-coded</t>
+    <t>codeValueSet</t>
   </si>
   <si>
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/cpg-rating-coded</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/codeValueSet</t>
   </si>
   <si>
     <t>Version</t>
@@ -42,15 +42,9 @@
     <t>Name</t>
   </si>
   <si>
-    <t>CPGRatingCoded</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
-    <t>CPG Rating Extension</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -60,75 +54,75 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2025-02-17T11:04:00+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>HL7 Belgium</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Code ValueSet</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>FHIR Version</t>
+  </si>
+  <si>
+    <t>4.0.1</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>complex-type</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>Base Definition</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2025-02-07T08:52:52+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Belgium</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Belgium</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>A clinician-friendly rating, or score, for the recommendation; patient-friendly if the recommendation is patient-facing.</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>FHIR Version</t>
-  </si>
-  <si>
-    <t>4.0.1</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>complex-type</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>Base Definition</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
     <t>Derivation</t>
   </si>
   <si>
@@ -138,10 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Resource</t>
-  </si>
-  <si>
-    <t>element:PlanDefinition.action</t>
+    <t>element:Element</t>
   </si>
   <si>
     <t>Structure.ID</t>
@@ -334,8 +325,8 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>CodeableConcept
-QuantityRangeRatio</t>
+    <t xml:space="preserve">canonical
+</t>
   </si>
   <si>
     <t>Value of extension</t>
@@ -479,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -523,155 +514,143 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -684,7 +663,7 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.71875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.91015625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="19.59765625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.59765625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
@@ -723,115 +702,115 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>2</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="F1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>73</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>75</v>
-      </c>
-      <c r="AI1" t="s" s="1">
-        <v>76</v>
-      </c>
-      <c r="AJ1" t="s" s="1">
-        <v>77</v>
-      </c>
-      <c r="AK1" t="s" s="1">
-        <v>78</v>
       </c>
     </row>
     <row r="2">
@@ -839,102 +818,102 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="L2" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="J2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L2" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="M2" t="s" s="2">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="R2" s="2"/>
       <c r="S2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="AH2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI2" t="s" s="2">
+      <c r="AK2" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="AJ2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -942,102 +921,102 @@
         <v>3</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="L3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N3" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L3" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -1045,102 +1024,102 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="R4" s="2"/>
       <c r="S4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AC4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AD4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AE4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AE4" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AH4" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK4" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK4" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -1148,104 +1127,104 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M5" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="N5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="O5" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="R5" s="2"/>
       <c r="S5" t="s" s="2">
         <v>5</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -1253,102 +1232,102 @@
         <v>3</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="R6" s="2"/>
       <c r="S6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="176">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>ID</t>
   </si>
   <si>
-    <t>codeValueSet</t>
+    <t>PSSRequest</t>
   </si>
   <si>
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/codeValueSet</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSRequest</t>
   </si>
   <si>
     <t>Version</t>
@@ -45,6 +45,9 @@
     <t>Title</t>
   </si>
   <si>
+    <t>PSS Request</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:15:32+00:00</t>
+    <t>2025-02-19T10:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Code ValueSet</t>
+    <t>A request for PSS (Prescriber Support System) suggestions.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -102,19 +105,16 @@
     <t>Kind</t>
   </si>
   <si>
-    <t>complex-type</t>
+    <t>logical</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -126,13 +126,7 @@
     <t>Derivation</t>
   </si>
   <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>Context</t>
-  </si>
-  <si>
-    <t>element:Element</t>
+    <t>specialization</t>
   </si>
   <si>
     <t>Structure.ID</t>
@@ -256,54 +250,289 @@
 </t>
   </si>
   <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>PSSRequest.recordedDate</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date
+</t>
+  </si>
+  <si>
+    <t>Date on which the information was recorded</t>
+  </si>
+  <si>
+    <t>PSSRequest.pssidentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Identifier of the exchange session</t>
+  </si>
+  <si>
+    <t>PSSRequest.examination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference
+</t>
+  </si>
+  <si>
+    <t>The ID of the examination the prescriber wants to prescribe</t>
+  </si>
+  <si>
+    <t>PSSRequest.indication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Indication that triggers the PSS request, from structured list or free text</t>
+  </si>
+  <si>
+    <t>PSSRequest.supportingInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Information useful for PSS proposals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>PSSRequest.supportingInfo.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>PSSRequest.supportingInfo.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>PSSRequest.supportingInfo.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>PSSRequest.supportingInfo.patientAge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age
+</t>
+  </si>
+  <si>
+    <t>Age of the patient</t>
+  </si>
+  <si>
+    <t>PSSRequest.supportingInfo.patientGender</t>
+  </si>
+  <si>
+    <t>Gender of the patient</t>
+  </si>
+  <si>
+    <t>PSSResponse</t>
+  </si>
+  <si>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponse</t>
+  </si>
+  <si>
+    <t>PSS Response</t>
+  </si>
+  <si>
+    <t>A response from PSS providing recommendations.</t>
+  </si>
+  <si>
+    <t>PSSResponse.recordedDate</t>
+  </si>
+  <si>
+    <t>PSSResponse.pssidentifier</t>
+  </si>
+  <si>
+    <t>PSSResponse.indication</t>
+  </si>
+  <si>
+    <t>Condition that triggered the PSS response</t>
+  </si>
+  <si>
+    <t>PSSResponse.status</t>
+  </si>
+  <si>
+    <t>Status of the response</t>
+  </si>
+  <si>
+    <t>PSSResponse.treatmentOptions</t>
+  </si>
+  <si>
+    <t>List of recommendations provided by PSS</t>
+  </si>
+  <si>
+    <t>PSSResponse.treatmentOptions.id</t>
+  </si>
+  <si>
+    <t>PSSResponse.treatmentOptions.extension</t>
+  </si>
+  <si>
+    <t>PSSResponse.treatmentOptions.modifierExtension</t>
+  </si>
+  <si>
+    <t>PSSResponse.treatmentOptions.identifier</t>
+  </si>
+  <si>
+    <t>Identifier of the recommendation</t>
+  </si>
+  <si>
+    <t>PSSResponse.treatmentOptions.instruction</t>
+  </si>
+  <si>
+    <t>Code of the examination</t>
+  </si>
+  <si>
+    <t>PSSResponse.treatmentOptions.scoreValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>PSS score value</t>
+  </si>
+  <si>
+    <t>PSSResponse.treatmentOptions.scoreRating</t>
+  </si>
+  <si>
+    <t>Color associated with the score (Red, Orange, Green)</t>
+  </si>
+  <si>
+    <t>PSSResponse.treatmentOptions.radiationExposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Radiation exposure associated with the response</t>
+  </si>
+  <si>
+    <t>PSSResponse.evidenceSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(ResearchStudy)
+</t>
+  </si>
+  <si>
+    <t>Link to a source (study, publication, etc.) for the PSS</t>
+  </si>
+  <si>
+    <t>codeValueSet</t>
+  </si>
+  <si>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/codeValueSet</t>
+  </si>
+  <si>
+    <t>Code ValueSet</t>
+  </si>
+  <si>
+    <t>complex-type</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>Context</t>
+  </si>
+  <si>
+    <t>element:Element</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>Extension.id</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Extension.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -333,10 +562,6 @@
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
   </si>
 </sst>
 </file>
@@ -470,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -521,104 +746,106 @@
       <c r="A6" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" t="s" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -646,11 +873,349 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>39</v>
+      <c r="A23" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -660,14 +1225,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="13.91015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.59765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.59765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="2" max="2" width="47.5546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="47.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="8.95703125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="21.21875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="5.4296875" customWidth="true" bestFit="true"/>
@@ -677,7 +1242,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="234.15234375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -695,122 +1260,122 @@
     <col min="30" max="30" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="17.21484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="47.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="10.5546875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>2</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>73</v>
-      </c>
-      <c r="AJ1" t="s" s="1">
-        <v>74</v>
-      </c>
-      <c r="AK1" t="s" s="1">
-        <v>75</v>
       </c>
     </row>
     <row r="2">
@@ -818,102 +1383,102 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L2" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="H2" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="L2" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="M2" t="s" s="2">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="R2" s="2"/>
       <c r="S2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI2" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="T2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="AH2" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI2" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AJ2" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
@@ -921,102 +1486,102 @@
         <v>3</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -1024,102 +1589,102 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="R4" s="2"/>
       <c r="S4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
@@ -1127,104 +1692,102 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>99</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="R5" s="2"/>
       <c r="S5" t="s" s="2">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -1232,102 +1795,2794 @@
         <v>3</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="R6" s="2"/>
       <c r="S6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="T6" t="s" s="2">
+      <c r="AJ6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK6" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="N7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R7" s="2"/>
+      <c r="S7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R8" s="2"/>
+      <c r="S8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="U6" t="s" s="2">
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="O9" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R9" s="2"/>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI9" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="V6" t="s" s="2">
+      <c r="AJ9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="W6" t="s" s="2">
+      <c r="I10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O10" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="P10" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Q10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R10" s="2"/>
+      <c r="S10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI10" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="X6" t="s" s="2">
+      <c r="AJ10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK10" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R11" s="2"/>
+      <c r="S11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R12" s="2"/>
+      <c r="S12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H13" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="I13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R13" s="2"/>
+      <c r="S13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI13" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AJ13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R14" s="2"/>
+      <c r="S14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R15" s="2"/>
+      <c r="S15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R16" s="2"/>
+      <c r="S16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R17" s="2"/>
+      <c r="S17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AA6" t="s" s="2">
+      <c r="I18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R18" s="2"/>
+      <c r="S18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AB6" t="s" s="2">
+      <c r="AJ18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R19" s="2"/>
+      <c r="S19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="P20" s="2"/>
+      <c r="Q20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R20" s="2"/>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AD6" t="s" s="2">
+      <c r="AJ20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AE6" t="s" s="2">
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R21" s="2"/>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AF6" t="s" s="2">
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R22" s="2"/>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R23" s="2"/>
+      <c r="S23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R24" s="2"/>
+      <c r="S24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R25" s="2"/>
+      <c r="S25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R26" s="2"/>
+      <c r="S26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R27" s="2"/>
+      <c r="S27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H28" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AG6" t="s" s="2">
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R28" s="2"/>
+      <c r="S28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R29" s="2"/>
+      <c r="S29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG29" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AH6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
+      <c r="AH29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R30" s="2"/>
+      <c r="S30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI30" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AK6" t="s" s="2">
-        <v>104</v>
+      <c r="AJ30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="P31" s="2"/>
+      <c r="Q31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R31" s="2"/>
+      <c r="S31" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="R32" s="2"/>
+      <c r="S32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12976" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13872" uniqueCount="1103">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:33:36+00:00</t>
+    <t>2025-02-26T15:37:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3340,6 +3340,125 @@
   </si>
   <si>
     <t>element:PlanDefinition.action</t>
+  </si>
+  <si>
+    <t>pss-relevant-age</t>
+  </si>
+  <si>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/pss-relevant-age</t>
+  </si>
+  <si>
+    <t>PSSRelevantAge</t>
+  </si>
+  <si>
+    <t>PSS Relevant Patien Age</t>
+  </si>
+  <si>
+    <t>The approximate, relevant age of the patient at the time of the search.</t>
+  </si>
+  <si>
+    <t>element:Patient</t>
+  </si>
+  <si>
+    <t>pss-structured-rating</t>
+  </si>
+  <si>
+    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/pss-structured-rating</t>
+  </si>
+  <si>
+    <t>PSSStructuredRating</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingType</t>
+  </si>
+  <si>
+    <t>ratingType</t>
+  </si>
+  <si>
+    <t>Volume in the body where radiation was delivered</t>
+  </si>
+  <si>
+    <t>A BodyStructure resource representing the body structure treated, for example, Chest Wall Lymph Nodes.</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingType.id</t>
+  </si>
+  <si>
+    <t>Extension.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingType.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingType.url</t>
+  </si>
+  <si>
+    <t>Extension.extension.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingType.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingValue</t>
+  </si>
+  <si>
+    <t>ratingValue</t>
+  </si>
+  <si>
+    <t>Total Radiation Dose Delivered</t>
+  </si>
+  <si>
+    <t>The total amount of radiation delivered to this volume within the scope of this dose delivery.</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingValue.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingValue.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingValue.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingValue.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+Ratio</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingText</t>
+  </si>
+  <si>
+    <t>ratingText</t>
+  </si>
+  <si>
+    <t>Number of Fractions Delivered</t>
+  </si>
+  <si>
+    <t>The number of fractions delivered to this volume.</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingText.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingText.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingText.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:ratingText.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
 </sst>
 </file>
@@ -3473,7 +3592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B223"/>
+  <dimension ref="A1:B270"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -5204,6 +5323,370 @@
         <v>1063</v>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B224" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B231" s="2"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B238" s="2"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B239" s="2"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B243" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B247" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B254" s="2"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B256" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B261" s="2"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B262" s="2"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B265" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>1063</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -5211,7 +5694,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK383"/>
+  <dimension ref="A1:AK408"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.921875" customWidth="true" bestFit="true"/>
@@ -45238,6 +45721,2597 @@
         <v>105</v>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="s" s="2">
+        <v>1064</v>
+      </c>
+      <c r="B384" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C384" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D384" s="2"/>
+      <c r="E384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F384" s="2"/>
+      <c r="G384" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H384" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L384" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M384" t="s" s="2">
+        <v>1067</v>
+      </c>
+      <c r="N384" t="s" s="2">
+        <v>1068</v>
+      </c>
+      <c r="O384" s="2"/>
+      <c r="P384" s="2"/>
+      <c r="Q384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R384" s="2"/>
+      <c r="S384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF384" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG384" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="AH384" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI384" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ384" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK384" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="2">
+        <v>1064</v>
+      </c>
+      <c r="B385" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C385" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="D385" s="2"/>
+      <c r="E385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F385" s="2"/>
+      <c r="G385" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H385" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L385" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M385" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N385" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O385" s="2"/>
+      <c r="P385" s="2"/>
+      <c r="Q385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R385" s="2"/>
+      <c r="S385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG385" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH385" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI385" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ385" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK385" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="2">
+        <v>1064</v>
+      </c>
+      <c r="B386" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C386" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="D386" s="2"/>
+      <c r="E386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F386" s="2"/>
+      <c r="G386" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H386" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L386" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M386" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="N386" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O386" s="2"/>
+      <c r="P386" s="2"/>
+      <c r="Q386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R386" s="2"/>
+      <c r="S386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC386" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AD386" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AE386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF386" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG386" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH386" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI386" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ386" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK386" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="2">
+        <v>1064</v>
+      </c>
+      <c r="B387" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C387" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="D387" s="2"/>
+      <c r="E387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F387" s="2"/>
+      <c r="G387" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H387" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L387" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M387" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N387" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O387" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="P387" s="2"/>
+      <c r="Q387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R387" s="2"/>
+      <c r="S387" t="s" s="2">
+        <v>1065</v>
+      </c>
+      <c r="T387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG387" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AH387" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI387" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ387" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK387" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="2">
+        <v>1064</v>
+      </c>
+      <c r="B388" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C388" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="D388" s="2"/>
+      <c r="E388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F388" s="2"/>
+      <c r="G388" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H388" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L388" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M388" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N388" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="O388" s="2"/>
+      <c r="P388" s="2"/>
+      <c r="Q388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R388" s="2"/>
+      <c r="S388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG388" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AH388" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI388" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ388" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK388" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B389" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C389" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D389" s="2"/>
+      <c r="E389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F389" s="2"/>
+      <c r="G389" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H389" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L389" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M389" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N389" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O389" s="2"/>
+      <c r="P389" s="2"/>
+      <c r="Q389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R389" s="2"/>
+      <c r="S389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF389" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG389" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="AH389" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI389" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ389" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK389" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B390" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C390" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="D390" s="2"/>
+      <c r="E390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F390" s="2"/>
+      <c r="G390" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H390" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L390" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M390" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N390" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O390" s="2"/>
+      <c r="P390" s="2"/>
+      <c r="Q390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R390" s="2"/>
+      <c r="S390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG390" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH390" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI390" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ390" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK390" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B391" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C391" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="D391" s="2"/>
+      <c r="E391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F391" s="2"/>
+      <c r="G391" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H391" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L391" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M391" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="N391" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O391" s="2"/>
+      <c r="P391" s="2"/>
+      <c r="Q391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R391" s="2"/>
+      <c r="S391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC391" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AD391" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AE391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF391" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG391" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH391" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI391" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ391" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK391" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B392" t="s" s="2">
+        <v>1073</v>
+      </c>
+      <c r="C392" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="D392" t="s" s="2">
+        <v>1074</v>
+      </c>
+      <c r="E392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F392" s="2"/>
+      <c r="G392" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H392" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I392" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="J392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L392" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M392" t="s" s="2">
+        <v>1075</v>
+      </c>
+      <c r="N392" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="O392" s="2"/>
+      <c r="P392" s="2"/>
+      <c r="Q392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R392" s="2"/>
+      <c r="S392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG392" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH392" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI392" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ392" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK392" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B393" t="s" s="2">
+        <v>1077</v>
+      </c>
+      <c r="C393" t="s" s="2">
+        <v>1078</v>
+      </c>
+      <c r="D393" s="2"/>
+      <c r="E393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F393" s="2"/>
+      <c r="G393" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H393" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L393" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M393" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N393" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O393" s="2"/>
+      <c r="P393" s="2"/>
+      <c r="Q393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R393" s="2"/>
+      <c r="S393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG393" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH393" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI393" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ393" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK393" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B394" t="s" s="2">
+        <v>1079</v>
+      </c>
+      <c r="C394" t="s" s="2">
+        <v>1080</v>
+      </c>
+      <c r="D394" s="2"/>
+      <c r="E394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F394" s="2"/>
+      <c r="G394" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H394" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L394" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M394" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="N394" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O394" s="2"/>
+      <c r="P394" s="2"/>
+      <c r="Q394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R394" s="2"/>
+      <c r="S394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC394" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AD394" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AE394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF394" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG394" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH394" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI394" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ394" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK394" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B395" t="s" s="2">
+        <v>1081</v>
+      </c>
+      <c r="C395" t="s" s="2">
+        <v>1082</v>
+      </c>
+      <c r="D395" s="2"/>
+      <c r="E395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F395" s="2"/>
+      <c r="G395" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H395" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L395" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M395" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N395" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O395" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="P395" s="2"/>
+      <c r="Q395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R395" s="2"/>
+      <c r="S395" t="s" s="2">
+        <v>1074</v>
+      </c>
+      <c r="T395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG395" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AH395" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI395" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ395" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK395" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B396" t="s" s="2">
+        <v>1083</v>
+      </c>
+      <c r="C396" t="s" s="2">
+        <v>1084</v>
+      </c>
+      <c r="D396" s="2"/>
+      <c r="E396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F396" s="2"/>
+      <c r="G396" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H396" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L396" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M396" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N396" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="O396" s="2"/>
+      <c r="P396" s="2"/>
+      <c r="Q396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R396" s="2"/>
+      <c r="S396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG396" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AH396" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI396" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ396" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK396" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B397" t="s" s="2">
+        <v>1085</v>
+      </c>
+      <c r="C397" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="D397" t="s" s="2">
+        <v>1086</v>
+      </c>
+      <c r="E397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F397" s="2"/>
+      <c r="G397" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H397" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I397" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="J397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L397" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M397" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="N397" t="s" s="2">
+        <v>1088</v>
+      </c>
+      <c r="O397" s="2"/>
+      <c r="P397" s="2"/>
+      <c r="Q397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R397" s="2"/>
+      <c r="S397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG397" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH397" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI397" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ397" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK397" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B398" t="s" s="2">
+        <v>1089</v>
+      </c>
+      <c r="C398" t="s" s="2">
+        <v>1078</v>
+      </c>
+      <c r="D398" s="2"/>
+      <c r="E398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F398" s="2"/>
+      <c r="G398" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H398" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L398" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M398" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N398" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O398" s="2"/>
+      <c r="P398" s="2"/>
+      <c r="Q398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R398" s="2"/>
+      <c r="S398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG398" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH398" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI398" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ398" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK398" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B399" t="s" s="2">
+        <v>1090</v>
+      </c>
+      <c r="C399" t="s" s="2">
+        <v>1080</v>
+      </c>
+      <c r="D399" s="2"/>
+      <c r="E399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F399" s="2"/>
+      <c r="G399" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H399" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L399" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M399" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="N399" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O399" s="2"/>
+      <c r="P399" s="2"/>
+      <c r="Q399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R399" s="2"/>
+      <c r="S399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC399" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AD399" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AE399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF399" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG399" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH399" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI399" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ399" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK399" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B400" t="s" s="2">
+        <v>1091</v>
+      </c>
+      <c r="C400" t="s" s="2">
+        <v>1082</v>
+      </c>
+      <c r="D400" s="2"/>
+      <c r="E400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F400" s="2"/>
+      <c r="G400" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H400" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L400" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M400" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N400" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O400" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="P400" s="2"/>
+      <c r="Q400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R400" s="2"/>
+      <c r="S400" t="s" s="2">
+        <v>1086</v>
+      </c>
+      <c r="T400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG400" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AH400" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI400" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ400" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK400" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B401" t="s" s="2">
+        <v>1092</v>
+      </c>
+      <c r="C401" t="s" s="2">
+        <v>1084</v>
+      </c>
+      <c r="D401" s="2"/>
+      <c r="E401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F401" s="2"/>
+      <c r="G401" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H401" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L401" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="M401" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N401" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="O401" s="2"/>
+      <c r="P401" s="2"/>
+      <c r="Q401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R401" s="2"/>
+      <c r="S401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG401" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AH401" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI401" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ401" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK401" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B402" t="s" s="2">
+        <v>1094</v>
+      </c>
+      <c r="C402" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="D402" t="s" s="2">
+        <v>1095</v>
+      </c>
+      <c r="E402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F402" s="2"/>
+      <c r="G402" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H402" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I402" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="J402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L402" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M402" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="N402" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="O402" s="2"/>
+      <c r="P402" s="2"/>
+      <c r="Q402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R402" s="2"/>
+      <c r="S402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG402" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH402" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI402" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ402" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK402" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B403" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="C403" t="s" s="2">
+        <v>1078</v>
+      </c>
+      <c r="D403" s="2"/>
+      <c r="E403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F403" s="2"/>
+      <c r="G403" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H403" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L403" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M403" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N403" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O403" s="2"/>
+      <c r="P403" s="2"/>
+      <c r="Q403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R403" s="2"/>
+      <c r="S403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG403" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH403" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI403" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ403" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK403" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B404" t="s" s="2">
+        <v>1099</v>
+      </c>
+      <c r="C404" t="s" s="2">
+        <v>1080</v>
+      </c>
+      <c r="D404" s="2"/>
+      <c r="E404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F404" s="2"/>
+      <c r="G404" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H404" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L404" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M404" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="N404" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O404" s="2"/>
+      <c r="P404" s="2"/>
+      <c r="Q404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R404" s="2"/>
+      <c r="S404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC404" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AD404" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AE404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF404" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG404" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH404" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI404" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ404" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK404" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B405" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="C405" t="s" s="2">
+        <v>1082</v>
+      </c>
+      <c r="D405" s="2"/>
+      <c r="E405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F405" s="2"/>
+      <c r="G405" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H405" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L405" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M405" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N405" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O405" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="P405" s="2"/>
+      <c r="Q405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R405" s="2"/>
+      <c r="S405" t="s" s="2">
+        <v>1095</v>
+      </c>
+      <c r="T405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG405" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AH405" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI405" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ405" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK405" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B406" t="s" s="2">
+        <v>1101</v>
+      </c>
+      <c r="C406" t="s" s="2">
+        <v>1084</v>
+      </c>
+      <c r="D406" s="2"/>
+      <c r="E406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F406" s="2"/>
+      <c r="G406" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H406" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L406" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M406" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N406" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="O406" s="2"/>
+      <c r="P406" s="2"/>
+      <c r="Q406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R406" s="2"/>
+      <c r="S406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG406" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AH406" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI406" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ406" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK406" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B407" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C407" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="D407" s="2"/>
+      <c r="E407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F407" s="2"/>
+      <c r="G407" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H407" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L407" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M407" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N407" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O407" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="P407" s="2"/>
+      <c r="Q407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R407" s="2"/>
+      <c r="S407" t="s" s="2">
+        <v>1071</v>
+      </c>
+      <c r="T407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG407" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AH407" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI407" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ407" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK407" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B408" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C408" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="D408" s="2"/>
+      <c r="E408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F408" s="2"/>
+      <c r="G408" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H408" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="L408" t="s" s="2">
+        <v>1102</v>
+      </c>
+      <c r="M408" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N408" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="O408" s="2"/>
+      <c r="P408" s="2"/>
+      <c r="Q408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R408" s="2"/>
+      <c r="S408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG408" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AH408" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI408" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ408" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK408" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:29:33+00:00</t>
+    <t>2025-03-06T11:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/CodeValueSet</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/CodeValueSet</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:18:44+00:00</t>
+    <t>2025-03-06T20:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,7 +351,7 @@
     <t>PSSCodedRating</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSCodedRating</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSCodedRating</t>
   </si>
   <si>
     <t>PSS Rating Extension</t>
@@ -373,7 +373,7 @@
     <t>PSSDataAcquisitionForm</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSDataAcquisitionForm</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSDataAcquisitionForm</t>
   </si>
   <si>
     <t>PSS Data Acquisition Form</t>
@@ -958,7 +958,7 @@
     <t>Questionnaire.item.extension:CodeValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/CodeValueSet}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/CodeValueSet}
 </t>
   </si>
   <si>
@@ -1399,7 +1399,7 @@
     <t>PSSPatient</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSPatient</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSPatient</t>
   </si>
   <si>
     <t>PSS anonymised Patient</t>
@@ -1452,7 +1452,7 @@
     <t>relevantAge</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSRelevantAge}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSRelevantAge}
 </t>
   </si>
   <si>
@@ -2238,7 +2238,7 @@
     <t>PSSRelevantAge</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSRelevantAge</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSRelevantAge</t>
   </si>
   <si>
     <t>element:Patient</t>
@@ -2251,7 +2251,7 @@
     <t>PSSRequest</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSRequest</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSRequest</t>
   </si>
   <si>
     <t>PSS Request</t>
@@ -2330,7 +2330,7 @@
     <t>PSSRequestBundle</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSRequestBundle</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSRequestBundle</t>
   </si>
   <si>
     <t>PSS Request Bundle</t>
@@ -2774,7 +2774,7 @@
     <t>PSSResponse</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponse</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponse</t>
   </si>
   <si>
     <t>PSS Response</t>
@@ -2857,7 +2857,7 @@
     <t>PSSResponseBundle</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponseBundle</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponseBundle</t>
   </si>
   <si>
     <t>PSS Response Bundle</t>
@@ -2869,7 +2869,7 @@
     <t>PSSResponseCommunicationRequest</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponseCommunicationRequest</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponseCommunicationRequest</t>
   </si>
   <si>
     <t>PSS Response Communication Request</t>
@@ -3340,7 +3340,7 @@
     <t>PSSResponseMedicationRequest</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponseMedicationRequest</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponseMedicationRequest</t>
   </si>
   <si>
     <t>PSS Response Medication Request</t>
@@ -3998,7 +3998,7 @@
     <t>PSSResponseRequestGroup</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponseRequestGroup</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponseRequestGroup</t>
   </si>
   <si>
     <t>PSS Response Request Group</t>
@@ -4561,7 +4561,7 @@
     <t>structured-rating</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSStructuredRating}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSStructuredRating}
 </t>
   </si>
   <si>
@@ -4661,7 +4661,7 @@
     <t>PSSResponseServiceRequest</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponseServiceRequest</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponseServiceRequest</t>
   </si>
   <si>
     <t>PSS Response Service Request</t>
@@ -5196,7 +5196,7 @@
     <t>PSSStructuredRating</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSStructuredRating</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSStructuredRating</t>
   </si>
   <si>
     <t>element:RequestGroup.action</t>
@@ -5241,7 +5241,7 @@
     <t>Extension.extension.value[x]</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/PSSRatingTypesVS</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/PSSRatingTypesVS</t>
   </si>
   <si>
     <t>Extension.extension:ratingValue</t>
@@ -7926,7 +7926,7 @@
     <col min="24" max="24" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="186.83203125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="78.05078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="71.296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T09:02:50+00:00</t>
+    <t>2025-03-07T12:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T12:27:18+00:00</t>
+    <t>2025-03-07T13:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:27:46+00:00</t>
+    <t>2025-03-11T13:06:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:06:04+00:00</t>
+    <t>2025-03-11T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:09:22+00:00</t>
+    <t>2025-03-11T13:27:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:27:28+00:00</t>
+    <t>2025-03-11T13:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:28:38+00:00</t>
+    <t>2025-03-11T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:29:42+00:00</t>
+    <t>2025-03-17T15:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17T15:05:50+00:00</t>
+    <t>2025-03-18T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T11:13:27+00:00</t>
+    <t>2025-03-20T15:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T15:00:12+00:00</t>
+    <t>2025-03-24T10:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:58:19+00:00</t>
+    <t>2025-03-24T11:01:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:08+00:00</t>
+    <t>2025-03-24T11:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17935" uniqueCount="1695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17937" uniqueCount="1695">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:18+00:00</t>
+    <t>2025-03-24T12:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5437,7 +5437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B316"/>
+  <dimension ref="A1:B317"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -5817,89 +5817,89 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s" s="1">
+      <c r="A49" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B49" t="s" s="1">
+      <c r="B50" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>114</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>12</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B56" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
@@ -5907,169 +5907,169 @@
         <v>18</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>117</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B63" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>117</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>36</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B70" t="s" s="2">
+      <c r="B71" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="s" s="1">
+    <row r="72">
+      <c r="A72" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B71" t="s" s="1">
+      <c r="B72" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>7</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>12</v>
+        <v>440</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B78" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
@@ -6077,169 +6077,169 @@
         <v>18</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>440</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B85" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>440</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>441</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>36</v>
+        <v>442</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B92" t="s" s="2">
+      <c r="B93" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="s" s="1">
+    <row r="94">
+      <c r="A94" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B93" t="s" s="1">
+      <c r="B94" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>708</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>7</v>
+        <v>709</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>708</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>457</v>
+        <v>708</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>12</v>
+        <v>457</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B100" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104">
@@ -6247,177 +6247,177 @@
         <v>18</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>458</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B107" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>458</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B115" t="s" s="2">
+      <c r="B116" t="s" s="2">
         <v>710</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="s" s="1">
+    <row r="117">
+      <c r="A117" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B116" t="s" s="1">
+      <c r="B117" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>712</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>7</v>
+        <v>713</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>712</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>12</v>
+        <v>714</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B123" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127">
@@ -6425,169 +6425,169 @@
         <v>18</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>715</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B130" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>715</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>716</v>
+        <v>28</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>36</v>
+        <v>717</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B137" t="s" s="2">
+      <c r="B138" t="s" s="2">
         <v>718</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="s" s="1">
+    <row r="139">
+      <c r="A139" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B138" t="s" s="1">
+      <c r="B139" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>738</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>7</v>
+        <v>739</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>738</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>12</v>
+        <v>740</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B145" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149">
@@ -6595,169 +6595,169 @@
         <v>18</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>741</v>
+        <v>22</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B152" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>741</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>742</v>
+        <v>118</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>36</v>
+        <v>743</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B159" t="s" s="2">
+      <c r="B160" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="s" s="1">
+    <row r="161">
+      <c r="A161" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B160" t="s" s="1">
+      <c r="B161" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>878</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>7</v>
+        <v>879</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>878</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>12</v>
+        <v>880</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B167" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="171">
@@ -6765,169 +6765,169 @@
         <v>18</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>881</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B174" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>881</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>716</v>
+        <v>28</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>879</v>
+        <v>716</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>717</v>
+        <v>879</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>36</v>
+        <v>717</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B181" t="s" s="2">
+      <c r="B182" t="s" s="2">
         <v>718</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="s" s="1">
+    <row r="183">
+      <c r="A183" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B182" t="s" s="1">
+      <c r="B183" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>905</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>7</v>
+        <v>906</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>905</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>12</v>
+        <v>907</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B189" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193">
@@ -6935,169 +6935,169 @@
         <v>18</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>908</v>
+        <v>22</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B196" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>908</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>742</v>
+        <v>118</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>36</v>
+        <v>743</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B203" t="s" s="2">
+      <c r="B204" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="s" s="1">
+    <row r="205">
+      <c r="A205" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B204" t="s" s="1">
+      <c r="B205" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B205" t="s" s="2">
-        <v>909</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>7</v>
+        <v>910</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>909</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>12</v>
+        <v>911</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B211" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B212" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="215">
@@ -7105,169 +7105,169 @@
         <v>18</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>912</v>
+        <v>22</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B218" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>912</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B220" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>913</v>
+        <v>118</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>36</v>
+        <v>914</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B225" t="s" s="2">
+      <c r="B226" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="s" s="1">
+    <row r="227">
+      <c r="A227" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B226" t="s" s="1">
+      <c r="B227" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>1059</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>7</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>1059</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>12</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B233" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237">
@@ -7275,169 +7275,169 @@
         <v>18</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>1062</v>
+        <v>22</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B240" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>1062</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B242" s="2"/>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>1063</v>
+        <v>118</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>36</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B247" t="s" s="2">
+      <c r="B248" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="s" s="1">
+    <row r="249">
+      <c r="A249" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B248" t="s" s="1">
+      <c r="B249" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>1271</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>7</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>1271</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>12</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B255" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B256" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="259">
@@ -7445,169 +7445,169 @@
         <v>18</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>1274</v>
+        <v>22</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B262" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>1274</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B264" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>1275</v>
+        <v>118</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>36</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B269" t="s" s="2">
+      <c r="B270" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="s" s="1">
+    <row r="271">
+      <c r="A271" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B270" t="s" s="1">
+      <c r="B271" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B271" t="s" s="2">
-        <v>1489</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>7</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>1489</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>1491</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>12</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B277" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B278" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="281">
@@ -7615,169 +7615,169 @@
         <v>18</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>1492</v>
+        <v>22</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B284" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>1492</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B286" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>1493</v>
+        <v>118</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>36</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B291" t="s" s="2">
+      <c r="B292" t="s" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" t="s" s="1">
+    <row r="293">
+      <c r="A293" t="s" s="1">
         <v>0</v>
       </c>
-      <c r="B292" t="s" s="1">
+      <c r="B293" t="s" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B293" t="s" s="2">
-        <v>1659</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>7</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>1659</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>1457</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>12</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B299" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B300" t="s" s="2">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="303">
@@ -7785,91 +7785,91 @@
         <v>18</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>938</v>
+        <v>22</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B306" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B306" t="s" s="2">
+        <v>938</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B308" t="s" s="2">
-        <v>28</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B308" s="2"/>
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>1661</v>
+        <v>38</v>
       </c>
     </row>
     <row r="315">
@@ -7877,7 +7877,7 @@
         <v>39</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="316">
@@ -7885,6 +7885,14 @@
         <v>39</v>
       </c>
       <c r="B316" t="s" s="2">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B317" t="s" s="2">
         <v>1663</v>
       </c>
     </row>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T12:21:29+00:00</t>
+    <t>2025-03-26T10:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-26T10:25:04+00:00</t>
+    <t>2025-04-06T05:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T05:59:28+00:00</t>
+    <t>2025-04-06T06:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T06:02:42+00:00</t>
+    <t>2025-04-10T08:21:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-10T08:21:04+00:00</t>
+    <t>2025-04-15T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-15T15:53:54+00:00</t>
+    <t>2025-04-16T11:48:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T11:48:10+00:00</t>
+    <t>2025-04-16T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,22 +60,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T11:48:51+00:00</t>
+    <t>2025-04-16T12:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:31:30+00:00</t>
+    <t>2025-04-16T12:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:36:28+00:00</t>
+    <t>2025-04-16T12:41:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:41:18+00:00</t>
+    <t>2025-04-16T13:08:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,22 +60,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T13:08:49+00:00</t>
+    <t>2025-04-17T08:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>HL7 Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
+    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:44:33+00:00</t>
+    <t>2025-04-17T09:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:22:19+00:00</t>
+    <t>2025-04-17T09:39:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:39:14+00:00</t>
+    <t>2025-04-17T11:28:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,22 +60,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T11:28:46+00:00</t>
+    <t>2025-04-28T07:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:30:14+00:00</t>
+    <t>2025-04-28T07:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:30:51+00:00</t>
+    <t>2025-04-28T07:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:00+00:00</t>
+    <t>2025-04-28T07:57:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:33+00:00</t>
+    <t>2025-04-28T07:57:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:44+00:00</t>
+    <t>2025-04-30T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:13:57+00:00</t>
+    <t>2025-04-30T14:16:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:16:07+00:00</t>
+    <t>2025-04-30T14:16:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:16:39+00:00</t>
+    <t>2025-05-06T09:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T11:05:16+00:00</t>
+    <t>2025-05-06T11:11:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T11:11:40+00:00</t>
+    <t>2025-05-12T10:14:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -4936,7 +4936,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred] and a valueset using LOINC Order codes is available [here](http://hl7.org/fhir/R4/valueset-diagnostic-requests.html).</t>
+    <t>Codes for tests or services that can be carried out</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
@@ -7983,7 +7983,7 @@
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="251.859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="144.1953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="61.125" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:50:51+00:00</t>
+    <t>2025-05-12T19:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:54:00+00:00</t>
+    <t>2025-05-13T10:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:10+00:00</t>
+    <t>2025-05-13T10:14:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:30+00:00</t>
+    <t>2025-05-13T11:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:53:59+00:00</t>
+    <t>2025-05-13T11:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:54:01+00:00</t>
+    <t>2025-05-13T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:55:17+00:00</t>
+    <t>2025-05-14T06:43:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:43:44+00:00</t>
+    <t>2025-05-14T06:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:09+00:00</t>
+    <t>2025-05-14T06:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:38+00:00</t>
+    <t>2025-05-14T06:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:56:25+00:00</t>
+    <t>2025-05-14T07:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:28:26+00:00</t>
+    <t>2025-05-14T07:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:16+00:00</t>
+    <t>2025-05-14T07:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:17+00:00</t>
+    <t>2025-05-14T07:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:38:16+00:00</t>
+    <t>2025-05-14T07:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:51:32+00:00</t>
+    <t>2025-05-14T07:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:52:33+00:00</t>
+    <t>2025-05-14T07:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:53:22+00:00</t>
+    <t>2025-05-14T08:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:06:44+00:00</t>
+    <t>2025-05-14T08:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:37:41+00:00</t>
+    <t>2025-05-14T14:59:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:59:57+00:00</t>
+    <t>2025-05-14T15:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:00:45+00:00</t>
+    <t>2025-05-14T15:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:07:35+00:00</t>
+    <t>2025-05-14T15:08:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:43:01+00:00</t>
+    <t>2025-05-22T14:52:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:52:21+00:00</t>
+    <t>2025-06-11T04:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1577,7 +1577,7 @@
     <t>PSSFeedbackModel.outcome</t>
   </si>
   <si>
-    <t>accepted, discarded, overridden</t>
+    <t>accepted, rejected, overridden</t>
   </si>
   <si>
     <t>PSSFeedbackModel.suggestionOutcome</t>
@@ -1604,13 +1604,13 @@
     <t>PSSFeedbackModel.suggestionOutcome.outcome</t>
   </si>
   <si>
-    <t>accepted or overridden</t>
+    <t>accepted, rejected or overridden</t>
   </si>
   <si>
     <t>PSSFeedbackModel.suggestionOutcome.overrideReason</t>
   </si>
   <si>
-    <t>The reason for overriding - code or text</t>
+    <t>The reason for rejecting or overriding - code or text</t>
   </si>
   <si>
     <t>PSSMedicationRequest</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-26T13:57:34+00:00</t>
+    <t>2025-07-16T16:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T16:47:23+00:00</t>
+    <t>2025-07-16T16:49:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
